--- a/public/templates/termo_fomento.xlsx
+++ b/public/templates/termo_fomento.xlsx
@@ -2,16 +2,16 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Orientacoes" sheetId="1" r:id="R0bd88f25be1b4322"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ajuste" sheetId="2" r:id="R0f6d933db5bc4b33"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Contratos" sheetId="3" r:id="R564f20bb0b614fd0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Naturezas_Contrato" sheetId="4" r:id="Rb4a7326e9b5a4b8c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Documentos_Fiscais" sheetId="5" r:id="Reb7c6aefb1e54494"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pagamentos" sheetId="6" r:id="Rceb9decf456141b0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Funcionarios" sheetId="7" r:id="R8ffcfbef9d6d42e7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Salarios" sheetId="8" r:id="R1bb7e95fb17342de"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Remuneracoes_Func" sheetId="9" r:id="R0fd9c292e9a74b50"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dicionario" sheetId="10" r:id="R2e6182266510427b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Orientacoes" sheetId="1" r:id="Rd6412750b7c2404f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ajuste" sheetId="2" r:id="R9b5e352bff374050"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Contratos" sheetId="3" r:id="R34c0e2ab2fc14037"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Naturezas_Contrato" sheetId="4" r:id="R0f3ace7bcab44669"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Documentos_Fiscais" sheetId="5" r:id="Rbe580426a94446bb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pagamentos" sheetId="6" r:id="Rbdbd31fa320f40b8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Funcionarios" sheetId="7" r:id="R00587491bc2241a4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Salarios" sheetId="8" r:id="Ra5a0ac949bee43c8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Remuneracoes_Func" sheetId="9" r:id="R6f5e308fcfb545a8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dicionario" sheetId="10" r:id="R3eb82ff66a6e4f0a"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -391,10 +391,10 @@
     </x:row>
     <x:row r="10" ht="26" customHeight="1">
       <x:c r="A10" s="1" t="str">
-        <x:v>CSV alternativo</x:v>
+        <x:v>Arquivo de carga</x:v>
       </x:c>
       <x:c r="B10" s="1" t="str">
-        <x:v>Um CSV UTF-8 por aba. Use o nome da aba como nome do arquivo. Ajuste.csv é obrigatório.</x:v>
+        <x:v>Envie somente um arquivo XLSX com todas as abas do ajuste.</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="26" customHeight="1">
